--- a/单位数据表.xlsx
+++ b/单位数据表.xlsx
@@ -550,32 +550,33 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>同高每格1支配力；上升或下降1级额外消耗1支配力（当前每格2点）。
-高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位。</t>
+高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位或障碍格。</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>近战攻击：消耗4支配力，攻击1格范围内的指定目标。
-造成2–4单体伤害，可指定友军。
+          <t>近战攻击：消耗8支配力，攻击1格范围内的指定目标。
+造成5–7单体伤害，可指定友军。
 仅能命中与攻击者高度差≤1级的单位；范围攻击逐个目标检查高度。</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>瞬移：消耗6支配力，到达自身6格范围内任一空格。
-可越过单位，不触发借机攻击；之后仍可继续行动。</t>
+可越过单位和障碍，但不能落在障碍格；不触发借机攻击，之后仍可继续行动。
+当头猛击：消耗8支配力，目标必须比自己低，且在普通攻击范围内。基础伤害10–14。守护转移不重复加成。近战仅能命中低1级的目标。沿用普通攻击形状和友伤规则，每个目标分别检查高度。</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>控制区：1格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
-不消耗资源，次数不限；每个敌方目标受到2–4伤害，不伤害友军。
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。每个敌方目标受到5–7伤害，不伤害友军。
 只覆盖和命中与攻击者高度差≤1级的格子及单位。</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>魂归主宰：死亡时恢复5点共享支配力，不超过20点上限。</t>
+          <t>魂归主宰：死亡时恢复5点共享支配力，不超过本关支配力上限。</t>
         </is>
       </c>
     </row>
@@ -596,31 +597,31 @@
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>同高每格1支配力；上升或下降1级额外消耗1支配力（当前每格2点）。
-高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位。</t>
+高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位或障碍格。</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>撕咬：消耗2支配力，攻击1格范围内的指定目标。
-造成1–2单体伤害，可指定友军。
+          <t>撕咬：消耗4支配力，攻击1格范围内的指定目标。
+造成3单体伤害，可指定友军。
 仅能命中与攻击者高度差≤1级的单位；范围攻击逐个目标检查高度。</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>当头猛击：消耗4支配力，目标必须比自己低，且在普通攻击范围内。基础伤害6。守护转移不重复加成。近战仅能命中低1级的目标。沿用普通攻击形状和友伤规则，每个目标分别检查高度。</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>控制区：1格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
-不消耗资源，次数不限；每个敌方目标受到1–2伤害，不伤害友军。
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。每个敌方目标受到3伤害，不伤害友军。
 只覆盖和命中与攻击者高度差≤1级的格子及单位。</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>魂归主宰：死亡时恢复5点共享支配力，不超过20点上限。</t>
+          <t>魂归主宰：死亡时恢复5点共享支配力，不超过本关支配力上限。</t>
         </is>
       </c>
     </row>
@@ -711,7 +712,7 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>同高每格1AP；上升或下降1级额外消耗1AP（当前每格2点）。
-高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位。</t>
+高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位或障碍格。</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -725,13 +726,13 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>当头猛击：消耗3AP，目标必须比自己低，且在普通攻击范围内。基础伤害2–6。每名相邻人类友军额外增加2伤害。守护转移不重复加成。近战仅能命中低1级的目标。沿用普通攻击形状和友伤规则，每个目标分别检查高度。</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>控制区：2格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
-不消耗资源，次数不限；每个敌方目标受到1–3伤害，不伤害友军。
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。每个敌方目标受到1–3伤害，不伤害友军。
 沿用穿刺形状：直线前1～2格范围伤害，非直线单体；跳过友军，不阻挡后方敌人受伤。
 只覆盖和命中与攻击者高度差≤1级的格子及单位。</t>
         </is>
@@ -759,7 +760,7 @@
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>同高每格1AP；上升或下降1级额外消耗1AP（当前每格2点）。
-高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位。</t>
+高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位或障碍格。</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -771,7 +772,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>当头猛击：消耗2AP，目标必须比自己低，且在普通攻击范围内。基础伤害2–6。每名相邻人类友军额外增加2伤害。守护转移不重复加成。射程内较低目标均可。沿用普通攻击形状和友伤规则，每个目标分别检查高度。</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -802,7 +803,7 @@
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>同高每格1AP；上升或下降1级额外消耗1AP（当前每格2点）。
-高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位。</t>
+高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位或障碍格。</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -817,13 +818,14 @@
           <t>守护：消耗3AP，持续至下次人类回合开始。
 相邻6格友军所受伤害全部转移到自己；友军微颤后闪白光、不扣血。
 双方都开启守护的盾兵互不保护；只开一方可保护未开启的一方。
-同一友军被多人守护时按部署顺序转移一次。范围伤害命中自己及友军时，两份都承担。</t>
+同一友军被多人守护时按部署顺序转移一次。范围伤害命中自己及友军时，两份都承担。
+当头猛击：消耗3AP，目标必须比自己低，且在普通攻击范围内。基础伤害2–4。每名相邻人类友军额外增加2伤害。守护转移不重复加成。近战仅能命中低1级的目标。沿用普通攻击形状和友伤规则，每个目标分别检查高度。</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>控制区：1格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
-不消耗资源，次数不限；每个敌方目标受到1–2伤害，不伤害友军。
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。每个敌方目标受到1–2伤害，不伤害友军。
 只覆盖和命中与攻击者高度差≤1级的格子及单位。</t>
         </is>
       </c>

--- a/单位数据表.xlsx
+++ b/单位数据表.xlsx
@@ -164,7 +164,7 @@
     <tableColumn id="3" name="行动资源"/>
     <tableColumn id="4" name="移动"/>
     <tableColumn id="5" name="攻击"/>
-    <tableColumn id="6" name="特殊动作"/>
+    <tableColumn id="6" name="优势动作 / 其他技能"/>
     <tableColumn id="7" name="借机攻击"/>
     <tableColumn id="8" name="特性"/>
   </tableColumns>
@@ -181,7 +181,7 @@
     <tableColumn id="3" name="行动资源"/>
     <tableColumn id="4" name="移动"/>
     <tableColumn id="5" name="攻击"/>
-    <tableColumn id="6" name="特殊动作"/>
+    <tableColumn id="6" name="优势动作 / 其他技能"/>
     <tableColumn id="7" name="借机攻击"/>
     <tableColumn id="8" name="特性"/>
   </tableColumns>
@@ -519,7 +519,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>特殊动作</t>
+          <t>优势动作 / 其他技能</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -564,13 +564,13 @@
         <is>
           <t>瞬移：消耗6支配力，到达自身6格范围内任一空格。
 可越过单位和障碍，但不能落在障碍格；不触发借机攻击，之后仍可继续行动。
-当头猛击：消耗8支配力，目标必须比自己低，且在普通攻击范围内。基础伤害10–14。守护转移不重复加成。近战仅能命中低1级的目标。沿用普通攻击形状和友伤规则，每个目标分别检查高度。</t>
+优势动作·当头猛击：消耗8支配力，自身高于目标，或敌方目标相邻六格内有至少3名存活己方单位（包括行动者）；目标仍须在普通攻击范围内。基础伤害10–14。守护转移不重复加成。近战高度差不得超过1级。沿用普通攻击形状和友伤规则，每个目标分别检查优势条件。</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>控制区：1格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
-不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。每个敌方目标受到5–7伤害，不伤害友军。
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。仅触发移动的敌人受到5–7单体伤害，不波及其他单位。
 只覆盖和命中与攻击者高度差≤1级的格子及单位。</t>
         </is>
       </c>
@@ -603,19 +603,19 @@
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>撕咬：消耗4支配力，攻击1格范围内的指定目标。
-造成3单体伤害，可指定友军。
+造成2–4单体伤害，可指定友军。
 仅能命中与攻击者高度差≤1级的单位；范围攻击逐个目标检查高度。</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>当头猛击：消耗4支配力，目标必须比自己低，且在普通攻击范围内。基础伤害6。守护转移不重复加成。近战仅能命中低1级的目标。沿用普通攻击形状和友伤规则，每个目标分别检查高度。</t>
+          <t>优势动作·当头猛击：消耗4支配力，自身高于目标，或敌方目标相邻六格内有至少3名存活己方单位（包括行动者）；目标仍须在普通攻击范围内。基础伤害4–8。守护转移不重复加成。近战高度差不得超过1级。沿用普通攻击形状和友伤规则，每个目标分别检查优势条件。</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>控制区：1格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
-不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。每个敌方目标受到3伤害，不伤害友军。
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。仅触发移动的敌人受到2–4单体伤害，不波及其他单位。
 只覆盖和命中与攻击者高度差≤1级的格子及单位。</t>
         </is>
       </c>
@@ -681,7 +681,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>特殊动作</t>
+          <t>优势动作 / 其他技能</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -706,7 +706,9 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>独立AP：每回合6点</t>
+          <t>独立AP：每回合6点。
+初始士气100；相邻六格敌人3–4名-20、5名-40、6名-80（可解除的状态惩罚）。2格内每名友军阵亡累计-20。HP小于等于20%时-20、初始人数阵亡过半时-20（状态惩罚，不重复叠加）。
+士气0时溃逃2个人类回合，只向随机可达右边缘移动，禁用攻击/守护/借机；到达右边缘离场，不算阵亡。士气0且六面被敌人包围时无法移动或恢复，解除包围后重新计算2个溺逃回合；再次完全被围则清空计时并保持士气0。未离场则基础士气恢复到80，再扣当前状态惩罚；仅低血量与阵亡过半生效时为40士气，包围惩罚另计。</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -726,14 +728,16 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>当头猛击：消耗3AP，目标必须比自己低，且在普通攻击范围内。基础伤害2–6。每名相邻人类友军额外增加2伤害。守护转移不重复加成。近战仅能命中低1级的目标。沿用普通攻击形状和友伤规则，每个目标分别检查高度。</t>
+          <t>优势动作·击退：3AP，范围1格单体，基础伤害2；自身高于目标，或敌方目标相邻六格内有至少3名存活己方单位（包括行动者）。近战高度差不得超过1级。
+目标后退1格，后方有障碍、任意单位、更高地势或越界则不移动，伤害仍结算。
+落到较低地势时另受每级2点坠落伤害；坠落不叠加众志成城。击退不触发借机攻击。</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>控制区：2格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
-不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。每个敌方目标受到1–3伤害，不伤害友军。
-沿用穿刺形状：直线前1～2格范围伤害，非直线单体；跳过友军，不阻挡后方敌人受伤。
+          <t>控制区：1格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。仅触发移动的敌人受到1–3单体伤害，不波及其他单位。
+不使用普通穿刺的直线范围伤害；直线与非直线目标均只命中触发者。
 只覆盖和命中与攻击者高度差≤1级的格子及单位。</t>
         </is>
       </c>
@@ -754,7 +758,9 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>独立AP：每回合6点</t>
+          <t>独立AP：每回合6点。
+初始士气100；相邻六格敌人3–4名-20、5名-40、6名-80（可解除的状态惩罚）。2格内每名友军阵亡累计-20。HP小于等于20%时-20、初始人数阵亡过半时-20（状态惩罚，不重复叠加）。
+士气0时溃逃2个人类回合，只向随机可达右边缘移动，禁用攻击/守护/借机；到达右边缘离场，不算阵亡。士气0且六面被敌人包围时无法移动或恢复，解除包围后重新计算2个溺逃回合；再次完全被围则清空计时并保持士气0。未离场则基础士气恢复到80，再扣当前状态惩罚；仅低血量与阵亡过半生效时为40士气，包围惩罚另计。</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -772,7 +778,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>当头猛击：消耗2AP，目标必须比自己低，且在普通攻击范围内。基础伤害2–6。每名相邻人类友军额外增加2伤害。守护转移不重复加成。射程内较低目标均可。沿用普通攻击形状和友伤规则，每个目标分别检查高度。</t>
+          <t>优势动作·当头猛击：消耗2AP，自身高于目标，或敌方目标相邻六格内有至少3名存活己方单位（包括行动者）；目标仍须在普通攻击范围内。基础伤害2–6。每名相邻人类友军额外增加2伤害。守护转移不重复加成。远程无高度差上限。沿用普通攻击形状和友伤规则，每个目标分别检查优势条件。</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -797,7 +803,9 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>独立AP：每回合6点</t>
+          <t>独立AP：每回合6点。
+初始士气100；相邻六格敌人3–4名-20、5名-40、6名-80（可解除的状态惩罚）。2格内每名友军阵亡累计-20。HP小于等于20%时-20、初始人数阵亡过半时-20（状态惩罚，不重复叠加）。
+士气0时溃逃2个人类回合，只向随机可达右边缘移动，禁用攻击/守护/借机；到达右边缘离场，不算阵亡。士气0且六面被敌人包围时无法移动或恢复，解除包围后重新计算2个溺逃回合；再次完全被围则清空计时并保持士气0。未离场则基础士气恢复到80，再扣当前状态惩罚；仅低血量与阵亡过半生效时为40士气，包围惩罚另计。</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -819,13 +827,13 @@
 相邻6格友军所受伤害全部转移到自己；友军微颤后闪白光、不扣血。
 双方都开启守护的盾兵互不保护；只开一方可保护未开启的一方。
 同一友军被多人守护时按部署顺序转移一次。范围伤害命中自己及友军时，两份都承担。
-当头猛击：消耗3AP，目标必须比自己低，且在普通攻击范围内。基础伤害2–4。每名相邻人类友军额外增加2伤害。守护转移不重复加成。近战仅能命中低1级的目标。沿用普通攻击形状和友伤规则，每个目标分别检查高度。</t>
+优势动作·当头猛击：消耗3AP，自身高于目标，或敌方目标相邻六格内有至少3名存活己方单位（包括行动者）；目标仍须在普通攻击范围内。基础伤害2–4。每名相邻人类友军额外增加2伤害。守护转移不重复加成。近战高度差不得超过1级。沿用普通攻击形状和友伤规则，每个目标分别检查优势条件。</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>控制区：1格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
-不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。每个敌方目标受到1–2伤害，不伤害友军。
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。仅触发移动的敌人受到1–2单体伤害，不波及其他单位。
 只覆盖和命中与攻击者高度差≤1级的格子及单位。</t>
         </is>
       </c>

--- a/单位数据表.xlsx
+++ b/单位数据表.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="己方" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,34 +12,53 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'己方'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'己方'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'己方'!$A$1:$H$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'敌人'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'敌人'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'敌人'!$A$1:$H$5</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
+      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="微软雅黑"/>
+      <charset val="1"/>
+      <family val="0"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="微软雅黑"/>
-      <color rgb="00243746"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <color rgb="FF243746"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -52,7 +71,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00243E50"/>
+        <fgColor rgb="FF243E50"/>
+        <bgColor rgb="FF243746"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,99 +85,153 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF243E50"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF243746"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF243E50"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF243746"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AlliedUnits" displayName="AlliedUnits" ref="A1:H3" headerRowCount="1">
-  <autoFilter ref="A1:H3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AlliedUnits" displayName="AlliedUnits" ref="A1:H7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H7"/>
   <tableColumns count="8">
     <tableColumn id="1" name="单位"/>
     <tableColumn id="2" name="生命值（HP）"/>
@@ -168,13 +242,12 @@
     <tableColumn id="7" name="借机攻击"/>
     <tableColumn id="8" name="特性"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EnemyUnits" displayName="EnemyUnits" ref="A1:H4" headerRowCount="1">
-  <autoFilter ref="A1:H4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EnemyUnits" displayName="EnemyUnits" ref="A1:H5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H5"/>
   <tableColumns count="8">
     <tableColumn id="1" name="单位"/>
     <tableColumn id="2" name="生命值（HP）"/>
@@ -185,46 +258,45 @@
     <tableColumn id="7" name="借机攻击"/>
     <tableColumn id="8" name="特性"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -232,402 +304,510 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="63" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="63" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" style="5" min="1" max="1"/>
+    <col width="17" customWidth="1" style="5" min="2" max="2"/>
+    <col width="25" customWidth="1" style="5" min="3" max="3"/>
+    <col width="33" customWidth="1" style="5" min="4" max="4"/>
+    <col width="63" customWidth="1" style="5" min="5" max="5"/>
+    <col width="44" customWidth="1" style="5" min="6" max="6"/>
+    <col width="63" customWidth="1" style="5" min="7" max="7"/>
+    <col width="44" customWidth="1" style="5" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="31.5" customHeight="1" s="6">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>生命值（HP）</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>行动资源</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>移动</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>优势动作 / 其他技能</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>借机攻击</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>特性</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="160" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="300" customHeight="1" s="6">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>吸血鬼</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>共享支配力</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>同高每格1支配力；上升或下降1级额外消耗1支配力（当前每格2点）。
 高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位或障碍格。</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>近战攻击：消耗8支配力，攻击1格范围内的指定目标。
-造成5–7单体伤害，可指定友军。
-仅能命中与攻击者高度差≤1级的单位；范围攻击逐个目标检查高度。</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>瞬移：消耗6支配力，到达自身6格范围内任一空格。
+造成7-9单体伤害，可指定友军。
+仅能命中与攻击者高度差≤1级的单位；范围攻击逐个目标检查高度。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>优势动作·猩红之吻：消耗8支配力，范围1格。
+自身高于目标，或敌方目标相邻六格内有至少3名存活己方单位（包括行动者）。
+基础伤害6点。恢复自身6生命，不超过20生命上限。
+其余沿用普通攻击的目标和友伤规则。近战高度差不得超过1级。
+瞬移：消耗6支配力，到达自身6格范围内任一空格。
 可越过单位和障碍，但不能落在障碍格；不触发借机攻击，之后仍可继续行动。
-优势动作·当头猛击：消耗8支配力，自身高于目标，或敌方目标相邻六格内有至少3名存活己方单位（包括行动者）；目标仍须在普通攻击范围内。基础伤害10–14。守护转移不重复加成。近战高度差不得超过1级。沿用普通攻击形状和友伤规则，每个目标分别检查优势条件。</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>控制区：1格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
-不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。仅触发移动的敌人受到5–7单体伤害，不波及其他单位。
-只覆盖和命中与攻击者高度差≤1级的格子及单位。</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。
+仅触发移动的敌人受到7–9点单体基础伤害，不波及其他单位。伤害数值与普通攻击一致。
+借机攻击仅同步伤害数值，不附带普通攻击的范围伤害、击退、冲锋等效果。只覆盖和命中高度差≤1级的目标。</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>魂归主宰：死亡时恢复5点共享支配力，不超过本关支配力上限。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="160" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="300" customHeight="1" s="6">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>僵尸</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>共享支配力</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>同高每格1支配力；上升或下降1级额外消耗1支配力（当前每格2点）。
 高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位或障碍格。</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>撕咬：消耗4支配力，攻击1格范围内的指定目标。
-造成2–4单体伤害，可指定友军。
-仅能命中与攻击者高度差≤1级的单位；范围攻击逐个目标检查高度。</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>优势动作·当头猛击：消耗4支配力，自身高于目标，或敌方目标相邻六格内有至少3名存活己方单位（包括行动者）；目标仍须在普通攻击范围内。基础伤害4–8。守护转移不重复加成。近战高度差不得超过1级。沿用普通攻击形状和友伤规则，每个目标分别检查优势条件。</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+造成3-5单体伤害，可指定友军。
+仅能命中与攻击者高度差≤1级的单位；范围攻击逐个目标检查高度。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>优势动作·疯狂啃噬 / Feeding Frenzy：消耗6支配力，范围1格。
+自身高于目标，或敌方目标相邻六格内有至少3名存活己方单位（包括行动者）。
+连续造成3次伤害，每次独立造成2-4点；目标死亡或战斗结束即停止。整次只扣一次消耗。
+其余沿用普通攻击的目标和友伤规则。近战高度差不得超过1级。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>控制区：1格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
-不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。仅触发移动的敌人受到2–4单体伤害，不波及其他单位。
-只覆盖和命中与攻击者高度差≤1级的格子及单位。</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。
+仅触发移动的敌人受到3–5点单体基础伤害，不波及其他单位。伤害数值与普通攻击一致。
+借机攻击仅同步伤害数值，不附带普通攻击的范围伤害、击退、冲锋等效果。只覆盖和命中高度差≤1级的目标。</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>魂归主宰：死亡时恢复5点共享支配力，不超过本关支配力上限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="300" customHeight="1" s="6">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>亡灵矛兵</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>共享支配力</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>同高每格1支配力；上升或下降1级额外消耗1支配力（当前每格2点）。
+高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位或障碍格。</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>穿刺：消耗3支配力，攻击2格范围内的指定目标。
+目标在六条直线方向上：对该方向前1～2格内的所有单位造成范围伤害，每个目标独立受到2伤害。
+目标不在直线上：仅对指定目标造成2伤害。
+可伤害友军。
+仅能命中与攻击者高度差≤1级的单位；范围攻击逐个目标检查高度。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>优势动作·击退：3支配力，范围1格单体，基础伤害2；自身高于目标，或敌方目标相邻六格内有至少3名存活己方单位（包括行动者）。近战高度差不得超过1级。
+目标后退1格，后方有障碍、任意单位、更高地势或越界则不移动，伤害仍结算。
+落到较低地势时另受每级2点坠落伤害；坠落不叠加众志成城。击退不触发借机攻击。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>控制区：1格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。
+仅触发移动的敌人受到2点单体基础伤害，不波及其他单位。伤害数值与普通攻击一致。
+借机攻击仅同步伤害数值，不附带普通攻击的范围伤害、击退、冲锋等效果。只覆盖和命中高度差≤1级的目标。</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>魂归主宰：死亡时恢复5点共享支配力，不超过本关支配力上限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="300" customHeight="1" s="6">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>亡灵弓兵</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>共享支配力</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>同高每格1支配力；上升或下降1级额外消耗1支配力（当前每格2点）。
+高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位或障碍格。</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>射击：消耗4支配力，攻击5格范围内的指定目标。
+造成2-6单体伤害，可指定友军。
+中间单位不阻挡，也不会受伤。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>优势动作·要害射击：消耗6支配力，范围5格。
+自身高于目标，或敌方目标相邻六格内有至少3名存活己方单位（包括行动者）。
+基础伤害9点。其余沿用普通攻击的目标和友伤规则。远程如果地方地势低于自己无高度差上限， 高于自己只能攻击高度差小于等于2的单位；中间单位不阻挡且不受伤。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>无（没有控制区，也没有借机攻击）</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>魂归主宰：死亡时恢复5点共享支配力，不超过本关支配力上限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="300" customHeight="1" s="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>亡灵盾兵</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>共享支配力</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>同高每格1支配力；上升或下降1级额外消耗1支配力（当前每格2点）。
+高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位或障碍格。</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>盾击：消耗6支配力，攻击1格范围内的指定目标。
+造成1单体伤害，并击退，可指定友军。
+仅能命中与攻击者高度差≤1级的单位；范围攻击逐个目标检查高度。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>优势动作·強力盾击：消耗6支配力，攻击1格范围内的指定目标。
+造成1单体伤害，并眩晕，可指定友军。
+守护：消耗6支配力，持续至下次所属阵营回合开始。
+相邻6格友军所受伤害全部转移到自己；友军微颤后闪白光、不扣血。
+双方都开启守护的盾兵互不保护；只开一方可保护未开启的一方。
+同一友军被多人守护时按部署顺序转移一次。范围伤害命中自己及友军时，两份都承担。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>控制区：1格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。
+仅触发移动的敌人受到1点单体基础伤害，不波及其他单位。伤害数值与普通攻击一致。
+借机攻击仅同步伤害数值，不附带普通攻击的范围伤害、击退、冲锋等效果。只覆盖和命中高度差≤1级的目标。</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>魂归主宰：死亡时恢复5点共享支配力，不超过本关支配力上限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="300" customHeight="1" s="6">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>亡灵骑士</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>共享支配力</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>同高每格1支配力；上升或下降1级额外消耗1支配力（当前每格2点）。
+高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位或障碍格。</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>骑士冲锋：整次消耗5支配力，直线移动恰好3格，不另收移动费。冲锋移动不触发借机攻击。
+到达后自动攻击正前方、左前方、右前方3格中的所有单位，含友军；每个目标基础5伤害，并向远离骑士方向击退1格。无目标则结束。
+不能穿过单位、障碍或相邻高差超过1级的地形；命中仍须高差≤1。击退后方为障碍、任意单位、更高地形或地图外时不位移，伤害仍结算。下降另结算每级2点坠落伤害，击退不触发借机。
+人类AI进攻时在命中敌人数多于友军数时冲锋，否则尝试换位寻找角度。
+需要离开有效敌方控制区时，优先用冲锋脱离，可冲向无目标地点；仍避免友伤占优的路线。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>优势动作·战争践踏：消耗6支配力，范围1，相邻指定单位单体（可指定友军）8伤害并施加击退一格， 如果目标被成功击退或者死亡则骑士移动至目标原来的格子。
+自身高于目标，或目标被至少3名己方单位包围；近战高差≤1。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>控制区：1格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。
+仅触发移动的敌人受到5点单体基础伤害，不波及其他单位。骑士借机攻击基础伤害固定5点。
+借机攻击仅同步伤害数值，不附带普通攻击的范围伤害、击退、冲锋等效果。只覆盖和命中高度差≤1级的目标。</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>精英。魂归主宰：死亡时恢复5点共享支配力，不超过本关支配力上限。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
@@ -636,216 +816,283 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="63" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="63" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" style="5" min="1" max="1"/>
+    <col width="17" customWidth="1" style="5" min="2" max="2"/>
+    <col width="25" customWidth="1" style="5" min="3" max="3"/>
+    <col width="33" customWidth="1" style="5" min="4" max="4"/>
+    <col width="63" customWidth="1" style="5" min="5" max="5"/>
+    <col width="44" customWidth="1" style="5" min="6" max="6"/>
+    <col width="63" customWidth="1" style="5" min="7" max="7"/>
+    <col width="44" customWidth="1" style="5" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="31.5" customHeight="1" s="6">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>生命值（HP）</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>行动资源</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>移动</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>优势动作 / 其他技能</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>借机攻击</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>特性</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="160" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="360" customHeight="1" s="6">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>矛兵</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>独立AP：每回合6点。
 初始士气100；相邻六格敌人3–4名-20、5名-40、6名-80（可解除的状态惩罚）。2格内每名友军阵亡累计-20。HP小于等于20%时-20、初始人数阵亡过半时-20（状态惩罚，不重复叠加）。
-士气0时溃逃2个人类回合，只向随机可达右边缘移动，禁用攻击/守护/借机；到达右边缘离场，不算阵亡。士气0且六面被敌人包围时无法移动或恢复，解除包围后重新计算2个溺逃回合；再次完全被围则清空计时并保持士气0。未离场则基础士气恢复到80，再扣当前状态惩罚；仅低血量与阵亡过半生效时为40士气，包围惩罚另计。</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+士气0时溃逃2个人类回合，只向随机可达右边缘移动，禁用攻击/守护/借机；到达右边缘离场，不算阵亡。士气0且六面被敌人包围时无法移动或恢复，解除包围后重新计算2个溃逃回合；再次完全被围则清空计时并保持士气0。未离场则基础士气恢复到80，再扣当前状态惩罚；仅低血量与阵亡过半生效时为40士气，包围惩罚另计。</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>同高每格1AP；上升或下降1级额外消耗1AP（当前每格2点）。
 高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位或障碍格。</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>穿刺：消耗3AP，攻击2格范围内的指定目标。
-目标在六条直线方向上：对该方向前1～2格内的所有单位造成范围伤害，每个目标独立受到1–3伤害。
-目标不在直线上：仅对指定目标造成1–3伤害。
+目标在六条直线方向上：对该方向前1～2格内的所有单位造成范围伤害，每个目标独立受到2伤害。
+目标不在直线上：仅对指定目标造成2伤害。
 可伤害友军。
-仅能命中与攻击者高度差≤1级的单位；范围攻击逐个目标检查高度。</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+仅能命中与攻击者高度差≤1级的单位；范围攻击逐个目标检查高度。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>优势动作·击退：3AP，范围1格单体，基础伤害2；自身高于目标，或敌方目标相邻六格内有至少3名存活己方单位（包括行动者）。近战高度差不得超过1级。
 目标后退1格，后方有障碍、任意单位、更高地势或越界则不移动，伤害仍结算。
-落到较低地势时另受每级2点坠落伤害；坠落不叠加众志成城。击退不触发借机攻击。</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+落到较低地势时另受每级2点坠落伤害；坠落不叠加众志成城。击退不触发借机攻击。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>控制区：1格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
-不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。仅触发移动的敌人受到1–3单体伤害，不波及其他单位。
-不使用普通穿刺的直线范围伤害；直线与非直线目标均只命中触发者。
-只覆盖和命中与攻击者高度差≤1级的格子及单位。</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。
+仅触发移动的敌人受到2点单体基础伤害，不波及其他单位。伤害数值与普通攻击一致。
+借机攻击仅同步伤害数值，不附带普通攻击的范围伤害、击退、冲锋等效果。只覆盖和命中高度差≤1级的目标。
+众志成城照常增加伤害。</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>众志成城：每有1名相邻六格内的存活人类友军，造成的伤害+1。普通攻击、借机攻击、范围攻击每个目标均适用；守护转移不重复加成。不再减免受到的伤害。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="160" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="360" customHeight="1" s="6">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>弓兵</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>独立AP：每回合6点。
 初始士气100；相邻六格敌人3–4名-20、5名-40、6名-80（可解除的状态惩罚）。2格内每名友军阵亡累计-20。HP小于等于20%时-20、初始人数阵亡过半时-20（状态惩罚，不重复叠加）。
-士气0时溃逃2个人类回合，只向随机可达右边缘移动，禁用攻击/守护/借机；到达右边缘离场，不算阵亡。士气0且六面被敌人包围时无法移动或恢复，解除包围后重新计算2个溺逃回合；再次完全被围则清空计时并保持士气0。未离场则基础士气恢复到80，再扣当前状态惩罚；仅低血量与阵亡过半生效时为40士气，包围惩罚另计。</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+士气0时溃逃2个人类回合，只向随机可达右边缘移动，禁用攻击/守护/借机；到达右边缘离场，不算阵亡。士气0且六面被敌人包围时无法移动或恢复，解除包围后重新计算2个溃逃回合；再次完全被围则清空计时并保持士气0。未离场则基础士气恢复到80，再扣当前状态惩罚；仅低血量与阵亡过半生效时为40士气，包围惩罚另计。</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>同高每格1AP；上升或下降1级额外消耗1AP（当前每格2点）。
 高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位或障碍格。</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>射击：消耗2AP，攻击5格范围内的指定目标。
-造成1–3单体伤害，可指定友军。
-中间单位不阻挡，也不会受伤。</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>优势动作·当头猛击：消耗2AP，自身高于目标，或敌方目标相邻六格内有至少3名存活己方单位（包括行动者）；目标仍须在普通攻击范围内。基础伤害2–6。每名相邻人类友军额外增加2伤害。守护转移不重复加成。远程无高度差上限。沿用普通攻击形状和友伤规则，每个目标分别检查优势条件。</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>无（没有控制区）</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>射击：消耗4AP，攻击5格范围内的指定目标。
+造成2-6单体伤害，可指定友军。
+中间单位不阻挡，也不会受伤。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>优势动作·要害射击：消耗6AP，范围5格。
+自身高于目标，或敌方目标相邻六格内有至少3名存活己方单位（包括行动者）。
+基础伤害9点。其余沿用普通攻击的目标和友伤规则。远程如果地方地势低于自己无高度差上限， 高于自己只能攻击高度差小于等于2的单位；中间单位不阻挡且不受伤。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>无（没有控制区，也没有借机攻击）</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>众志成城：每有1名相邻六格内的存活人类友军，造成的伤害+1。普通攻击、借机攻击、范围攻击每个目标均适用；守护转移不重复加成。不再减免受到的伤害。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="220" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="4" ht="360" customHeight="1" s="6">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>盾兵</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>独立AP：每回合6点。
 初始士气100；相邻六格敌人3–4名-20、5名-40、6名-80（可解除的状态惩罚）。2格内每名友军阵亡累计-20。HP小于等于20%时-20、初始人数阵亡过半时-20（状态惩罚，不重复叠加）。
-士气0时溃逃2个人类回合，只向随机可达右边缘移动，禁用攻击/守护/借机；到达右边缘离场，不算阵亡。士气0且六面被敌人包围时无法移动或恢复，解除包围后重新计算2个溺逃回合；再次完全被围则清空计时并保持士气0。未离场则基础士气恢复到80，再扣当前状态惩罚；仅低血量与阵亡过半生效时为40士气，包围惩罚另计。</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+士气0时溃逃2个人类回合，只向随机可达右边缘移动，禁用攻击/守护/借机；到达右边缘离场，不算阵亡。士气0且六面被敌人包围时无法移动或恢复，解除包围后重新计算2个溃逃回合；再次完全被围则清空计时并保持士气0。未离场则基础士气恢复到80，再扣当前状态惩罚；仅低血量与阵亡过半生效时为40士气，包围惩罚另计。</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>同高每格1AP；上升或下降1级额外消耗1AP（当前每格2点）。
 高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位或障碍格。</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>盾击：消耗3AP，攻击1格范围内的指定目标。
-造成1–2单体伤害，可指定友军。
-仅能命中与攻击者高度差≤1级的单位；范围攻击逐个目标检查高度。</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>守护：消耗3AP，持续至下次人类回合开始。
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>盾击：消耗6AP，攻击1格范围内的指定目标。
+造成1单体伤害，并击退，可指定友军。
+仅能命中与攻击者高度差≤1级的单位；范围攻击逐个目标检查高度。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>优势动作·強力盾击：消耗6AP，攻击1格范围内的指定目标。
+造成1单体伤害，并眩晕，可指定友军。
+守护：消耗6AP，持续至下次所属阵营回合开始。
 相邻6格友军所受伤害全部转移到自己；友军微颤后闪白光、不扣血。
 双方都开启守护的盾兵互不保护；只开一方可保护未开启的一方。
 同一友军被多人守护时按部署顺序转移一次。范围伤害命中自己及友军时，两份都承担。
-优势动作·当头猛击：消耗3AP，自身高于目标，或敌方目标相邻六格内有至少3名存活己方单位（包括行动者）；目标仍须在普通攻击范围内。基础伤害2–4。每名相邻人类友军额外增加2伤害。守护转移不重复加成。近战高度差不得超过1级。沿用普通攻击形状和友伤规则，每个目标分别检查优势条件。</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>控制区：1格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
-不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。仅触发移动的敌人受到1–2单体伤害，不波及其他单位。
-只覆盖和命中与攻击者高度差≤1级的格子及单位。</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。
+仅触发移动的敌人受到1点单体基础伤害，不波及其他单位。伤害数值与普通攻击一致。
+借机攻击仅同步伤害数值，不附带普通攻击的范围伤害、击退、冲锋等效果。只覆盖和命中高度差≤1级的目标。
+众志成城照常增加伤害。</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>众志成城：每有1名相邻六格内的存活人类友军，造成的伤害+1。普通攻击、借机攻击、范围攻击每个目标均适用；守护转移不重复加成。不再减免受到的伤害。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="360" customHeight="1" s="6">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>骑士</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>独立AP：每回合12点。
+初始士气100；相邻六格敌人3–4名-20、5名-40、6名-80（可解除的状态惩罚）。2格内每名友军阵亡累计-20。HP小于等于20%时-20、初始人数阵亡过半时-20（状态惩罚，不重复叠加）。
+士气0时溃逃2个人类回合，只向随机可达右边缘移动，禁用攻击/守护/借机；到达右边缘离场，不算阵亡。士气0且六面被敌人包围时无法移动或恢复，解除包围后重新计算2个溃逃回合；再次完全被围则清空计时并保持士气0。未离场则基础士气恢复到80，再扣当前状态惩罚；仅低血量与阵亡过半生效时为40士气，包围惩罚另计。</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>同高每格1AP；上升或下降1级额外消耗1AP（当前每格2点）。
+高度差超过1级不可步行跨越；可连续移动，不能穿越其他单位或障碍格。</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>骑士冲锋：整次消耗5AP，直线移动恰好3格，不另收移动费。冲锋移动不触发借机攻击。
+到达后自动攻击正前方、左前方、右前方3格中的所有单位，含友军；每个目标基础5伤害，并向远离骑士方向击退1格。无目标则结束。
+不能穿过单位、障碍或相邻高差超过1级的地形；命中仍须高差≤1。击退后方为障碍、任意单位、更高地形或地图外时不位移，伤害仍结算。下降另结算每级2点坠落伤害，击退不触发借机。
+人类AI进攻时在命中敌人数多于友军数时冲锋，否则尝试换位寻找角度。
+需要离开有效敌方控制区时，优先用冲锋脱离，可冲向无目标地点；仍避免友伤占优的路线。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>优势动作·战争践踏：消耗6AP，范围1，相邻指定单位单体（可指定友军）8伤害并施加击退一格， 如果目标被成功击退或者死亡则骑士移动至目标原来的格子。
+自身高于目标，或目标被至少3名己方单位包围；近战高差≤1。
+主动攻击均可指定友军；范围攻击覆盖的友军同样受到伤害。</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>控制区：1格。敌人从区域内继续移动或离开时，在离开旧格前触发；走入不触发。
+不消耗资源，每个单位仅可触发1次，在自身所属阵营回合开始时恢复；触发后红色范围消失。
+仅触发移动的敌人受到5点单体基础伤害，不波及其他单位。骑士借机攻击基础伤害固定5点。
+借机攻击仅同步伤害数值，不附带普通攻击的范围伤害、击退、冲锋等效果。只覆盖和命中高度差≤1级的目标。
+众志成城照常增加伤害。</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>众志成城：每有1名相邻六格内的存活人类友军，造成的伤害+1。普通攻击、借机攻击、范围攻击每个目标均适用；守护转移不重复加成。不再减免受到的伤害。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
